--- a/web/public/forms/pumjil-gwanri-gyehoek.xlsx
+++ b/web/public/forms/pumjil-gwanri-gyehoek.xlsx
@@ -8,9 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="품질관리계획서 표지·목차" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성 예시" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'품질관리계획서 표지·목차'!$A$1:$X$39</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'작성 예시'!$A$1:$X$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -18,8 +20,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="6">
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="#,##0;[Red]-#,##0;&quot;&quot;"/>
+    <numFmt numFmtId="165" formatCode="yyyy&quot;년&quot; m&quot;월&quot; d&quot;일&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0;;&quot;&quot;"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
+  </numFmts>
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,32 +38,53 @@
       <name val="맑은 고딕"/>
       <b val="1"/>
       <color rgb="000F203F"/>
-      <sz val="10.5"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <color rgb="00222222"/>
+      <color rgb="006B7280"/>
       <sz val="8.5"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="000F203F"/>
+      <color rgb="00111827"/>
       <sz val="19"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="000F203F"/>
+      <color rgb="001F2937"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <color rgb="00222222"/>
+      <color rgb="00000000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="001F2937"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="001F2937"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -65,12 +93,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F6F8FC"/>
+        <fgColor rgb="00F3F5F9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EEF3FB"/>
+        <fgColor rgb="00E8EEF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEF4FC"/>
       </patternFill>
     </fill>
   </fills>
@@ -84,23 +117,23 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </left>
       <right style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </right>
       <top style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -109,32 +142,56 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -501,7 +558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:X42"/>
+  <dimension ref="A1:X43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3.6" customWidth="1" min="1" max="1"/>
@@ -530,15 +587,15 @@
     <col width="3.6" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵   |   k-conmap.com   무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">← 이 1행을 지우고 쓰셔도 됩니다   </t>
+          <t xml:space="preserve">← 이 1행을 지우고 쓰셔도 됩니다  </t>
         </is>
       </c>
     </row>
@@ -562,7 +619,7 @@
       <c r="D5" s="5" t="n"/>
       <c r="E5" s="5" t="n"/>
       <c r="F5" s="5" t="n"/>
-      <c r="G5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="n"/>
       <c r="H5" s="5" t="n"/>
       <c r="I5" s="5" t="n"/>
       <c r="J5" s="5" t="n"/>
@@ -592,7 +649,7 @@
       <c r="D6" s="5" t="n"/>
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="5" t="n"/>
-      <c r="G6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="n"/>
       <c r="H6" s="5" t="n"/>
       <c r="I6" s="5" t="n"/>
       <c r="J6" s="5" t="n"/>
@@ -622,7 +679,7 @@
       <c r="D7" s="5" t="n"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
-      <c r="G7" s="6" t="inlineStr"/>
+      <c r="G7" s="7" t="n"/>
       <c r="H7" s="5" t="n"/>
       <c r="I7" s="5" t="n"/>
       <c r="J7" s="5" t="n"/>
@@ -652,7 +709,7 @@
       <c r="D8" s="5" t="n"/>
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
-      <c r="G8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="n"/>
       <c r="H8" s="5" t="n"/>
       <c r="I8" s="5" t="n"/>
       <c r="J8" s="5" t="n"/>
@@ -682,7 +739,7 @@
       <c r="D9" s="5" t="n"/>
       <c r="E9" s="5" t="n"/>
       <c r="F9" s="5" t="n"/>
-      <c r="G9" s="6" t="inlineStr"/>
+      <c r="G9" s="8" t="n"/>
       <c r="H9" s="5" t="n"/>
       <c r="I9" s="5" t="n"/>
       <c r="J9" s="5" t="n"/>
@@ -713,7 +770,7 @@
       <c r="D11" s="5" t="n"/>
       <c r="E11" s="5" t="n"/>
       <c r="F11" s="5" t="n"/>
-      <c r="G11" s="6" t="inlineStr"/>
+      <c r="G11" s="6" t="n"/>
       <c r="H11" s="5" t="n"/>
       <c r="I11" s="5" t="n"/>
       <c r="J11" s="5" t="n"/>
@@ -743,7 +800,7 @@
       <c r="D12" s="5" t="n"/>
       <c r="E12" s="5" t="n"/>
       <c r="F12" s="5" t="n"/>
-      <c r="G12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="n"/>
       <c r="H12" s="5" t="n"/>
       <c r="I12" s="5" t="n"/>
       <c r="J12" s="5" t="n"/>
@@ -773,7 +830,7 @@
       <c r="D13" s="5" t="n"/>
       <c r="E13" s="5" t="n"/>
       <c r="F13" s="5" t="n"/>
-      <c r="G13" s="6" t="inlineStr"/>
+      <c r="G13" s="6" t="n"/>
       <c r="H13" s="5" t="n"/>
       <c r="I13" s="5" t="n"/>
       <c r="J13" s="5" t="n"/>
@@ -794,7 +851,7 @@
     </row>
     <row r="14" ht="6" customHeight="1"/>
     <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>■ 목  차</t>
         </is>
@@ -802,13 +859,13 @@
     </row>
     <row r="16" ht="6" customHeight="1"/>
     <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>장</t>
         </is>
       </c>
       <c r="B17" s="5" t="n"/>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C17" s="10" t="inlineStr">
         <is>
           <t>제        목</t>
         </is>
@@ -831,7 +888,7 @@
       <c r="S17" s="5" t="n"/>
       <c r="T17" s="5" t="n"/>
       <c r="U17" s="5" t="n"/>
-      <c r="V17" s="8" t="inlineStr">
+      <c r="V17" s="10" t="inlineStr">
         <is>
           <t>면</t>
         </is>
@@ -840,9 +897,12 @@
       <c r="X17" s="5" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="9" t="inlineStr"/>
+      <c r="A18" s="11">
+        <f>IF(C18="","",COUNTA(C18:C18))</f>
+        <v/>
+      </c>
       <c r="B18" s="5" t="n"/>
-      <c r="C18" s="9" t="inlineStr"/>
+      <c r="C18" s="12" t="n"/>
       <c r="D18" s="5" t="n"/>
       <c r="E18" s="5" t="n"/>
       <c r="F18" s="5" t="n"/>
@@ -861,14 +921,17 @@
       <c r="S18" s="5" t="n"/>
       <c r="T18" s="5" t="n"/>
       <c r="U18" s="5" t="n"/>
-      <c r="V18" s="9" t="inlineStr"/>
+      <c r="V18" s="13" t="n"/>
       <c r="W18" s="5" t="n"/>
       <c r="X18" s="5" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="9" t="inlineStr"/>
+      <c r="A19" s="11">
+        <f>IF(C19="","",COUNTA(C18:C19))</f>
+        <v/>
+      </c>
       <c r="B19" s="5" t="n"/>
-      <c r="C19" s="9" t="inlineStr"/>
+      <c r="C19" s="12" t="n"/>
       <c r="D19" s="5" t="n"/>
       <c r="E19" s="5" t="n"/>
       <c r="F19" s="5" t="n"/>
@@ -887,14 +950,17 @@
       <c r="S19" s="5" t="n"/>
       <c r="T19" s="5" t="n"/>
       <c r="U19" s="5" t="n"/>
-      <c r="V19" s="9" t="inlineStr"/>
+      <c r="V19" s="13" t="n"/>
       <c r="W19" s="5" t="n"/>
       <c r="X19" s="5" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="9" t="inlineStr"/>
+      <c r="A20" s="11">
+        <f>IF(C20="","",COUNTA(C18:C20))</f>
+        <v/>
+      </c>
       <c r="B20" s="5" t="n"/>
-      <c r="C20" s="9" t="inlineStr"/>
+      <c r="C20" s="12" t="n"/>
       <c r="D20" s="5" t="n"/>
       <c r="E20" s="5" t="n"/>
       <c r="F20" s="5" t="n"/>
@@ -913,14 +979,17 @@
       <c r="S20" s="5" t="n"/>
       <c r="T20" s="5" t="n"/>
       <c r="U20" s="5" t="n"/>
-      <c r="V20" s="9" t="inlineStr"/>
+      <c r="V20" s="13" t="n"/>
       <c r="W20" s="5" t="n"/>
       <c r="X20" s="5" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="9" t="inlineStr"/>
+      <c r="A21" s="11">
+        <f>IF(C21="","",COUNTA(C18:C21))</f>
+        <v/>
+      </c>
       <c r="B21" s="5" t="n"/>
-      <c r="C21" s="9" t="inlineStr"/>
+      <c r="C21" s="12" t="n"/>
       <c r="D21" s="5" t="n"/>
       <c r="E21" s="5" t="n"/>
       <c r="F21" s="5" t="n"/>
@@ -939,14 +1008,17 @@
       <c r="S21" s="5" t="n"/>
       <c r="T21" s="5" t="n"/>
       <c r="U21" s="5" t="n"/>
-      <c r="V21" s="9" t="inlineStr"/>
+      <c r="V21" s="13" t="n"/>
       <c r="W21" s="5" t="n"/>
       <c r="X21" s="5" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="9" t="inlineStr"/>
+      <c r="A22" s="11">
+        <f>IF(C22="","",COUNTA(C18:C22))</f>
+        <v/>
+      </c>
       <c r="B22" s="5" t="n"/>
-      <c r="C22" s="9" t="inlineStr"/>
+      <c r="C22" s="12" t="n"/>
       <c r="D22" s="5" t="n"/>
       <c r="E22" s="5" t="n"/>
       <c r="F22" s="5" t="n"/>
@@ -965,14 +1037,17 @@
       <c r="S22" s="5" t="n"/>
       <c r="T22" s="5" t="n"/>
       <c r="U22" s="5" t="n"/>
-      <c r="V22" s="9" t="inlineStr"/>
+      <c r="V22" s="13" t="n"/>
       <c r="W22" s="5" t="n"/>
       <c r="X22" s="5" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="9" t="inlineStr"/>
+      <c r="A23" s="11">
+        <f>IF(C23="","",COUNTA(C18:C23))</f>
+        <v/>
+      </c>
       <c r="B23" s="5" t="n"/>
-      <c r="C23" s="9" t="inlineStr"/>
+      <c r="C23" s="12" t="n"/>
       <c r="D23" s="5" t="n"/>
       <c r="E23" s="5" t="n"/>
       <c r="F23" s="5" t="n"/>
@@ -991,14 +1066,17 @@
       <c r="S23" s="5" t="n"/>
       <c r="T23" s="5" t="n"/>
       <c r="U23" s="5" t="n"/>
-      <c r="V23" s="9" t="inlineStr"/>
+      <c r="V23" s="13" t="n"/>
       <c r="W23" s="5" t="n"/>
       <c r="X23" s="5" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="9" t="inlineStr"/>
+      <c r="A24" s="11">
+        <f>IF(C24="","",COUNTA(C18:C24))</f>
+        <v/>
+      </c>
       <c r="B24" s="5" t="n"/>
-      <c r="C24" s="9" t="inlineStr"/>
+      <c r="C24" s="12" t="n"/>
       <c r="D24" s="5" t="n"/>
       <c r="E24" s="5" t="n"/>
       <c r="F24" s="5" t="n"/>
@@ -1017,14 +1095,17 @@
       <c r="S24" s="5" t="n"/>
       <c r="T24" s="5" t="n"/>
       <c r="U24" s="5" t="n"/>
-      <c r="V24" s="9" t="inlineStr"/>
+      <c r="V24" s="13" t="n"/>
       <c r="W24" s="5" t="n"/>
       <c r="X24" s="5" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="9" t="inlineStr"/>
+      <c r="A25" s="11">
+        <f>IF(C25="","",COUNTA(C18:C25))</f>
+        <v/>
+      </c>
       <c r="B25" s="5" t="n"/>
-      <c r="C25" s="9" t="inlineStr"/>
+      <c r="C25" s="12" t="n"/>
       <c r="D25" s="5" t="n"/>
       <c r="E25" s="5" t="n"/>
       <c r="F25" s="5" t="n"/>
@@ -1043,14 +1124,17 @@
       <c r="S25" s="5" t="n"/>
       <c r="T25" s="5" t="n"/>
       <c r="U25" s="5" t="n"/>
-      <c r="V25" s="9" t="inlineStr"/>
+      <c r="V25" s="13" t="n"/>
       <c r="W25" s="5" t="n"/>
       <c r="X25" s="5" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="9" t="inlineStr"/>
+      <c r="A26" s="11">
+        <f>IF(C26="","",COUNTA(C18:C26))</f>
+        <v/>
+      </c>
       <c r="B26" s="5" t="n"/>
-      <c r="C26" s="9" t="inlineStr"/>
+      <c r="C26" s="12" t="n"/>
       <c r="D26" s="5" t="n"/>
       <c r="E26" s="5" t="n"/>
       <c r="F26" s="5" t="n"/>
@@ -1069,14 +1153,17 @@
       <c r="S26" s="5" t="n"/>
       <c r="T26" s="5" t="n"/>
       <c r="U26" s="5" t="n"/>
-      <c r="V26" s="9" t="inlineStr"/>
+      <c r="V26" s="13" t="n"/>
       <c r="W26" s="5" t="n"/>
       <c r="X26" s="5" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="9" t="inlineStr"/>
+      <c r="A27" s="11">
+        <f>IF(C27="","",COUNTA(C18:C27))</f>
+        <v/>
+      </c>
       <c r="B27" s="5" t="n"/>
-      <c r="C27" s="9" t="inlineStr"/>
+      <c r="C27" s="12" t="n"/>
       <c r="D27" s="5" t="n"/>
       <c r="E27" s="5" t="n"/>
       <c r="F27" s="5" t="n"/>
@@ -1095,14 +1182,17 @@
       <c r="S27" s="5" t="n"/>
       <c r="T27" s="5" t="n"/>
       <c r="U27" s="5" t="n"/>
-      <c r="V27" s="9" t="inlineStr"/>
+      <c r="V27" s="13" t="n"/>
       <c r="W27" s="5" t="n"/>
       <c r="X27" s="5" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="9" t="inlineStr"/>
+      <c r="A28" s="11">
+        <f>IF(C28="","",COUNTA(C18:C28))</f>
+        <v/>
+      </c>
       <c r="B28" s="5" t="n"/>
-      <c r="C28" s="9" t="inlineStr"/>
+      <c r="C28" s="12" t="n"/>
       <c r="D28" s="5" t="n"/>
       <c r="E28" s="5" t="n"/>
       <c r="F28" s="5" t="n"/>
@@ -1121,14 +1211,17 @@
       <c r="S28" s="5" t="n"/>
       <c r="T28" s="5" t="n"/>
       <c r="U28" s="5" t="n"/>
-      <c r="V28" s="9" t="inlineStr"/>
+      <c r="V28" s="13" t="n"/>
       <c r="W28" s="5" t="n"/>
       <c r="X28" s="5" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="9" t="inlineStr"/>
+      <c r="A29" s="11">
+        <f>IF(C29="","",COUNTA(C18:C29))</f>
+        <v/>
+      </c>
       <c r="B29" s="5" t="n"/>
-      <c r="C29" s="9" t="inlineStr"/>
+      <c r="C29" s="12" t="n"/>
       <c r="D29" s="5" t="n"/>
       <c r="E29" s="5" t="n"/>
       <c r="F29" s="5" t="n"/>
@@ -1147,14 +1240,17 @@
       <c r="S29" s="5" t="n"/>
       <c r="T29" s="5" t="n"/>
       <c r="U29" s="5" t="n"/>
-      <c r="V29" s="9" t="inlineStr"/>
+      <c r="V29" s="13" t="n"/>
       <c r="W29" s="5" t="n"/>
       <c r="X29" s="5" t="n"/>
     </row>
     <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="9" t="inlineStr"/>
+      <c r="A30" s="11">
+        <f>IF(C30="","",COUNTA(C18:C30))</f>
+        <v/>
+      </c>
       <c r="B30" s="5" t="n"/>
-      <c r="C30" s="9" t="inlineStr"/>
+      <c r="C30" s="12" t="n"/>
       <c r="D30" s="5" t="n"/>
       <c r="E30" s="5" t="n"/>
       <c r="F30" s="5" t="n"/>
@@ -1173,14 +1269,17 @@
       <c r="S30" s="5" t="n"/>
       <c r="T30" s="5" t="n"/>
       <c r="U30" s="5" t="n"/>
-      <c r="V30" s="9" t="inlineStr"/>
+      <c r="V30" s="13" t="n"/>
       <c r="W30" s="5" t="n"/>
       <c r="X30" s="5" t="n"/>
     </row>
     <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="9" t="inlineStr"/>
+      <c r="A31" s="11">
+        <f>IF(C31="","",COUNTA(C18:C31))</f>
+        <v/>
+      </c>
       <c r="B31" s="5" t="n"/>
-      <c r="C31" s="9" t="inlineStr"/>
+      <c r="C31" s="12" t="n"/>
       <c r="D31" s="5" t="n"/>
       <c r="E31" s="5" t="n"/>
       <c r="F31" s="5" t="n"/>
@@ -1199,14 +1298,17 @@
       <c r="S31" s="5" t="n"/>
       <c r="T31" s="5" t="n"/>
       <c r="U31" s="5" t="n"/>
-      <c r="V31" s="9" t="inlineStr"/>
+      <c r="V31" s="13" t="n"/>
       <c r="W31" s="5" t="n"/>
       <c r="X31" s="5" t="n"/>
     </row>
     <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="9" t="inlineStr"/>
+      <c r="A32" s="11">
+        <f>IF(C32="","",COUNTA(C18:C32))</f>
+        <v/>
+      </c>
       <c r="B32" s="5" t="n"/>
-      <c r="C32" s="9" t="inlineStr"/>
+      <c r="C32" s="12" t="n"/>
       <c r="D32" s="5" t="n"/>
       <c r="E32" s="5" t="n"/>
       <c r="F32" s="5" t="n"/>
@@ -1225,14 +1327,17 @@
       <c r="S32" s="5" t="n"/>
       <c r="T32" s="5" t="n"/>
       <c r="U32" s="5" t="n"/>
-      <c r="V32" s="9" t="inlineStr"/>
+      <c r="V32" s="13" t="n"/>
       <c r="W32" s="5" t="n"/>
       <c r="X32" s="5" t="n"/>
     </row>
     <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="9" t="inlineStr"/>
+      <c r="A33" s="11">
+        <f>IF(C33="","",COUNTA(C18:C33))</f>
+        <v/>
+      </c>
       <c r="B33" s="5" t="n"/>
-      <c r="C33" s="9" t="inlineStr"/>
+      <c r="C33" s="12" t="n"/>
       <c r="D33" s="5" t="n"/>
       <c r="E33" s="5" t="n"/>
       <c r="F33" s="5" t="n"/>
@@ -1251,59 +1356,79 @@
       <c r="S33" s="5" t="n"/>
       <c r="T33" s="5" t="n"/>
       <c r="U33" s="5" t="n"/>
-      <c r="V33" s="9" t="inlineStr"/>
+      <c r="V33" s="13" t="n"/>
       <c r="W33" s="5" t="n"/>
       <c r="X33" s="5" t="n"/>
     </row>
     <row r="34" ht="6" customHeight="1"/>
     <row r="35" ht="10" customHeight="1"/>
     <row r="36" ht="26" customHeight="1">
-      <c r="A36" s="10" t="inlineStr">
-        <is>
-          <t>년        월        일</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="K37" s="11" t="inlineStr">
+      <c r="A36" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          년        월        일</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="15" t="inlineStr"/>
+      <c r="K37" s="16" t="inlineStr">
         <is>
           <t>품질관리자</t>
         </is>
       </c>
-      <c r="S37" s="10" t="inlineStr">
+      <c r="Q37" s="17" t="n"/>
+      <c r="U37" s="18" t="inlineStr">
         <is>
           <t>(서명 또는 인)</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="K38" s="11" t="inlineStr">
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="15" t="inlineStr"/>
+      <c r="K38" s="16" t="inlineStr">
         <is>
           <t>현장대리인</t>
         </is>
       </c>
-      <c r="S38" s="10" t="inlineStr">
+      <c r="Q38" s="17" t="n"/>
+      <c r="U38" s="18" t="inlineStr">
         <is>
           <t>(서명 또는 인)</t>
         </is>
       </c>
     </row>
     <row r="39" ht="6" customHeight="1"/>
-    <row r="42">
-      <c r="A42" s="12" t="inlineStr">
-        <is>
-          <t>발주기관이 정한 서식이 있으면 그 서식을 사용하세요. 이 줄과 1행은 인쇄 전에 지우셔도 됩니다.</t>
+    <row r="41" ht="34" customHeight="1">
+      <c r="A41" s="19" t="inlineStr">
+        <is>
+          <t>목차는 «건설공사 품질관리 업무지침»(국토교통부 고시) 품질관리계획서 작성기준의 항목 차례입니다 — 발주기관 요구에 맞춰 고쳐 쓰세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="34" customHeight="1">
+      <c r="A42" s="19" t="inlineStr">
+        <is>
+          <t>노란 칸 = 요율·기준값(발주기관 기준으로 고쳐 씀) · 옅은 하늘색 칸 = 자동 계산(지우지 마세요) · 뒤 시트에 «작성 예시» 가 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="19.5" customHeight="1">
+      <c r="A43" s="19" t="inlineStr">
+        <is>
+          <t>발주기관이 정한 서식이 있으면 그 서식을 쓰세요. 이 줄과 1행은 지워도 됩니다.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="77">
+  <mergeCells count="83">
     <mergeCell ref="V24:X24"/>
     <mergeCell ref="C23:U23"/>
+    <mergeCell ref="U38:X38"/>
     <mergeCell ref="A3:X3"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="C18:U18"/>
     <mergeCell ref="A27:B27"/>
+    <mergeCell ref="K38:P38"/>
     <mergeCell ref="V22:X22"/>
     <mergeCell ref="A13:F13"/>
     <mergeCell ref="A33:B33"/>
@@ -1315,30 +1440,33 @@
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="V23:X23"/>
     <mergeCell ref="C22:U22"/>
-    <mergeCell ref="K38:R38"/>
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="G7:X7"/>
+    <mergeCell ref="A38:J38"/>
     <mergeCell ref="C32:U32"/>
     <mergeCell ref="V27:X27"/>
     <mergeCell ref="A42:X42"/>
+    <mergeCell ref="Q37:T37"/>
     <mergeCell ref="V25:X25"/>
     <mergeCell ref="C24:U24"/>
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="C33:U33"/>
+    <mergeCell ref="K37:P37"/>
     <mergeCell ref="A9:F9"/>
     <mergeCell ref="C26:U26"/>
     <mergeCell ref="G9:X9"/>
     <mergeCell ref="V17:X17"/>
+    <mergeCell ref="Q38:T38"/>
     <mergeCell ref="A11:F11"/>
     <mergeCell ref="C25:U25"/>
     <mergeCell ref="G11:X11"/>
     <mergeCell ref="A15:X15"/>
     <mergeCell ref="V20:X20"/>
     <mergeCell ref="V29:X29"/>
-    <mergeCell ref="S38:X38"/>
     <mergeCell ref="V31:X31"/>
+    <mergeCell ref="A41:X41"/>
     <mergeCell ref="G13:X13"/>
     <mergeCell ref="V32:X32"/>
     <mergeCell ref="A8:F8"/>
@@ -1348,12 +1476,1086 @@
     <mergeCell ref="V18:X18"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="V33:X33"/>
-    <mergeCell ref="K37:R37"/>
+    <mergeCell ref="U37:X37"/>
     <mergeCell ref="V19:X19"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="V28:X28"/>
     <mergeCell ref="C27:U27"/>
-    <mergeCell ref="S37:X37"/>
+    <mergeCell ref="C17:U17"/>
+    <mergeCell ref="G6:X6"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="V30:X30"/>
+    <mergeCell ref="C19:U19"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C28:U28"/>
+    <mergeCell ref="G5:X5"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C30:U30"/>
+    <mergeCell ref="A43:X43"/>
+    <mergeCell ref="C29:U29"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A37:J37"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C31:U31"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="M1:X1"/>
+    <mergeCell ref="C21:U21"/>
+    <mergeCell ref="A36:X36"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="G8:X8"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00F59E0B"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:X41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3.6" customWidth="1" min="1" max="1"/>
+    <col width="3.6" customWidth="1" min="2" max="2"/>
+    <col width="3.6" customWidth="1" min="3" max="3"/>
+    <col width="3.6" customWidth="1" min="4" max="4"/>
+    <col width="3.6" customWidth="1" min="5" max="5"/>
+    <col width="3.6" customWidth="1" min="6" max="6"/>
+    <col width="3.6" customWidth="1" min="7" max="7"/>
+    <col width="3.6" customWidth="1" min="8" max="8"/>
+    <col width="3.6" customWidth="1" min="9" max="9"/>
+    <col width="3.6" customWidth="1" min="10" max="10"/>
+    <col width="3.6" customWidth="1" min="11" max="11"/>
+    <col width="3.6" customWidth="1" min="12" max="12"/>
+    <col width="3.6" customWidth="1" min="13" max="13"/>
+    <col width="3.6" customWidth="1" min="14" max="14"/>
+    <col width="3.6" customWidth="1" min="15" max="15"/>
+    <col width="3.6" customWidth="1" min="16" max="16"/>
+    <col width="3.6" customWidth="1" min="17" max="17"/>
+    <col width="3.6" customWidth="1" min="18" max="18"/>
+    <col width="3.6" customWidth="1" min="19" max="19"/>
+    <col width="3.6" customWidth="1" min="20" max="20"/>
+    <col width="3.6" customWidth="1" min="21" max="21"/>
+    <col width="3.6" customWidth="1" min="22" max="22"/>
+    <col width="3.6" customWidth="1" min="23" max="23"/>
+    <col width="3.6" customWidth="1" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+        </is>
+      </c>
+      <c r="M1" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="6" customHeight="1"/>
+    <row r="3" ht="38" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>품 질 관 리 계 획 서</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="10" customHeight="1"/>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  공 사 명</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>가나지구 배수로 정비공사</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+      <c r="P5" s="5" t="n"/>
+      <c r="Q5" s="5" t="n"/>
+      <c r="R5" s="5" t="n"/>
+      <c r="S5" s="5" t="n"/>
+      <c r="T5" s="5" t="n"/>
+      <c r="U5" s="5" t="n"/>
+      <c r="V5" s="5" t="n"/>
+      <c r="W5" s="5" t="n"/>
+      <c r="X5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  발 주 기 관</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>가나시 건설과</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
+      <c r="P6" s="5" t="n"/>
+      <c r="Q6" s="5" t="n"/>
+      <c r="R6" s="5" t="n"/>
+      <c r="S6" s="5" t="n"/>
+      <c r="T6" s="5" t="n"/>
+      <c r="U6" s="5" t="n"/>
+      <c r="V6" s="5" t="n"/>
+      <c r="W6" s="5" t="n"/>
+      <c r="X6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  계 약 금 액</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="7" t="n">
+        <v>963241000</v>
+      </c>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="5" t="n"/>
+      <c r="L7" s="5" t="n"/>
+      <c r="M7" s="5" t="n"/>
+      <c r="N7" s="5" t="n"/>
+      <c r="O7" s="5" t="n"/>
+      <c r="P7" s="5" t="n"/>
+      <c r="Q7" s="5" t="n"/>
+      <c r="R7" s="5" t="n"/>
+      <c r="S7" s="5" t="n"/>
+      <c r="T7" s="5" t="n"/>
+      <c r="U7" s="5" t="n"/>
+      <c r="V7" s="5" t="n"/>
+      <c r="W7" s="5" t="n"/>
+      <c r="X7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  공        기</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>2026. 3. 9. ~ 2026. 12. 31. (298일)</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="n"/>
+      <c r="K8" s="5" t="n"/>
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
+      <c r="P8" s="5" t="n"/>
+      <c r="Q8" s="5" t="n"/>
+      <c r="R8" s="5" t="n"/>
+      <c r="S8" s="5" t="n"/>
+      <c r="T8" s="5" t="n"/>
+      <c r="U8" s="5" t="n"/>
+      <c r="V8" s="5" t="n"/>
+      <c r="W8" s="5" t="n"/>
+      <c r="X8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  작 성 일 자</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="8" t="n">
+        <v>46294</v>
+      </c>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="5" t="n"/>
+      <c r="K9" s="5" t="n"/>
+      <c r="L9" s="5" t="n"/>
+      <c r="M9" s="5" t="n"/>
+      <c r="N9" s="5" t="n"/>
+      <c r="O9" s="5" t="n"/>
+      <c r="P9" s="5" t="n"/>
+      <c r="Q9" s="5" t="n"/>
+      <c r="R9" s="5" t="n"/>
+      <c r="S9" s="5" t="n"/>
+      <c r="T9" s="5" t="n"/>
+      <c r="U9" s="5" t="n"/>
+      <c r="V9" s="5" t="n"/>
+      <c r="W9" s="5" t="n"/>
+      <c r="X9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="6" customHeight="1"/>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  작 성 부 서</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>예시건설(주) 가나지구 현장</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="n"/>
+      <c r="I11" s="5" t="n"/>
+      <c r="J11" s="5" t="n"/>
+      <c r="K11" s="5" t="n"/>
+      <c r="L11" s="5" t="n"/>
+      <c r="M11" s="5" t="n"/>
+      <c r="N11" s="5" t="n"/>
+      <c r="O11" s="5" t="n"/>
+      <c r="P11" s="5" t="n"/>
+      <c r="Q11" s="5" t="n"/>
+      <c r="R11" s="5" t="n"/>
+      <c r="S11" s="5" t="n"/>
+      <c r="T11" s="5" t="n"/>
+      <c r="U11" s="5" t="n"/>
+      <c r="V11" s="5" t="n"/>
+      <c r="W11" s="5" t="n"/>
+      <c r="X11" s="5" t="n"/>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  품질관리자</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>한품질(건설재료시험기사)</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="n"/>
+      <c r="I12" s="5" t="n"/>
+      <c r="J12" s="5" t="n"/>
+      <c r="K12" s="5" t="n"/>
+      <c r="L12" s="5" t="n"/>
+      <c r="M12" s="5" t="n"/>
+      <c r="N12" s="5" t="n"/>
+      <c r="O12" s="5" t="n"/>
+      <c r="P12" s="5" t="n"/>
+      <c r="Q12" s="5" t="n"/>
+      <c r="R12" s="5" t="n"/>
+      <c r="S12" s="5" t="n"/>
+      <c r="T12" s="5" t="n"/>
+      <c r="U12" s="5" t="n"/>
+      <c r="V12" s="5" t="n"/>
+      <c r="W12" s="5" t="n"/>
+      <c r="X12" s="5" t="n"/>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  검토·승인 이력</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>2026. 3. 16. 제출 → 3. 23. 감리 승인</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="n"/>
+      <c r="I13" s="5" t="n"/>
+      <c r="J13" s="5" t="n"/>
+      <c r="K13" s="5" t="n"/>
+      <c r="L13" s="5" t="n"/>
+      <c r="M13" s="5" t="n"/>
+      <c r="N13" s="5" t="n"/>
+      <c r="O13" s="5" t="n"/>
+      <c r="P13" s="5" t="n"/>
+      <c r="Q13" s="5" t="n"/>
+      <c r="R13" s="5" t="n"/>
+      <c r="S13" s="5" t="n"/>
+      <c r="T13" s="5" t="n"/>
+      <c r="U13" s="5" t="n"/>
+      <c r="V13" s="5" t="n"/>
+      <c r="W13" s="5" t="n"/>
+      <c r="X13" s="5" t="n"/>
+    </row>
+    <row r="14" ht="6" customHeight="1"/>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>■ 목  차</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="6" customHeight="1"/>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>장</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>제        목</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
+      <c r="I17" s="5" t="n"/>
+      <c r="J17" s="5" t="n"/>
+      <c r="K17" s="5" t="n"/>
+      <c r="L17" s="5" t="n"/>
+      <c r="M17" s="5" t="n"/>
+      <c r="N17" s="5" t="n"/>
+      <c r="O17" s="5" t="n"/>
+      <c r="P17" s="5" t="n"/>
+      <c r="Q17" s="5" t="n"/>
+      <c r="R17" s="5" t="n"/>
+      <c r="S17" s="5" t="n"/>
+      <c r="T17" s="5" t="n"/>
+      <c r="U17" s="5" t="n"/>
+      <c r="V17" s="10" t="inlineStr">
+        <is>
+          <t>면</t>
+        </is>
+      </c>
+      <c r="W17" s="5" t="n"/>
+      <c r="X17" s="5" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="11">
+        <f>IF(C18="","",COUNTA(C18:C18))</f>
+        <v/>
+      </c>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>건설공사 정보</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="n"/>
+      <c r="I18" s="5" t="n"/>
+      <c r="J18" s="5" t="n"/>
+      <c r="K18" s="5" t="n"/>
+      <c r="L18" s="5" t="n"/>
+      <c r="M18" s="5" t="n"/>
+      <c r="N18" s="5" t="n"/>
+      <c r="O18" s="5" t="n"/>
+      <c r="P18" s="5" t="n"/>
+      <c r="Q18" s="5" t="n"/>
+      <c r="R18" s="5" t="n"/>
+      <c r="S18" s="5" t="n"/>
+      <c r="T18" s="5" t="n"/>
+      <c r="U18" s="5" t="n"/>
+      <c r="V18" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="W18" s="5" t="n"/>
+      <c r="X18" s="5" t="n"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="11">
+        <f>IF(C19="","",COUNTA(C18:C19))</f>
+        <v/>
+      </c>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>현장 품질방침 및 품질목표</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="n"/>
+      <c r="I19" s="5" t="n"/>
+      <c r="J19" s="5" t="n"/>
+      <c r="K19" s="5" t="n"/>
+      <c r="L19" s="5" t="n"/>
+      <c r="M19" s="5" t="n"/>
+      <c r="N19" s="5" t="n"/>
+      <c r="O19" s="5" t="n"/>
+      <c r="P19" s="5" t="n"/>
+      <c r="Q19" s="5" t="n"/>
+      <c r="R19" s="5" t="n"/>
+      <c r="S19" s="5" t="n"/>
+      <c r="T19" s="5" t="n"/>
+      <c r="U19" s="5" t="n"/>
+      <c r="V19" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="W19" s="5" t="n"/>
+      <c r="X19" s="5" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="11">
+        <f>IF(C20="","",COUNTA(C18:C20))</f>
+        <v/>
+      </c>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>책임 및 권한</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n"/>
+      <c r="I20" s="5" t="n"/>
+      <c r="J20" s="5" t="n"/>
+      <c r="K20" s="5" t="n"/>
+      <c r="L20" s="5" t="n"/>
+      <c r="M20" s="5" t="n"/>
+      <c r="N20" s="5" t="n"/>
+      <c r="O20" s="5" t="n"/>
+      <c r="P20" s="5" t="n"/>
+      <c r="Q20" s="5" t="n"/>
+      <c r="R20" s="5" t="n"/>
+      <c r="S20" s="5" t="n"/>
+      <c r="T20" s="5" t="n"/>
+      <c r="U20" s="5" t="n"/>
+      <c r="V20" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="W20" s="5" t="n"/>
+      <c r="X20" s="5" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="11">
+        <f>IF(C21="","",COUNTA(C18:C21))</f>
+        <v/>
+      </c>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>문서관리</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
+      <c r="I21" s="5" t="n"/>
+      <c r="J21" s="5" t="n"/>
+      <c r="K21" s="5" t="n"/>
+      <c r="L21" s="5" t="n"/>
+      <c r="M21" s="5" t="n"/>
+      <c r="N21" s="5" t="n"/>
+      <c r="O21" s="5" t="n"/>
+      <c r="P21" s="5" t="n"/>
+      <c r="Q21" s="5" t="n"/>
+      <c r="R21" s="5" t="n"/>
+      <c r="S21" s="5" t="n"/>
+      <c r="T21" s="5" t="n"/>
+      <c r="U21" s="5" t="n"/>
+      <c r="V21" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="W21" s="5" t="n"/>
+      <c r="X21" s="5" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="11">
+        <f>IF(C22="","",COUNTA(C18:C22))</f>
+        <v/>
+      </c>
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>기록관리</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n"/>
+      <c r="I22" s="5" t="n"/>
+      <c r="J22" s="5" t="n"/>
+      <c r="K22" s="5" t="n"/>
+      <c r="L22" s="5" t="n"/>
+      <c r="M22" s="5" t="n"/>
+      <c r="N22" s="5" t="n"/>
+      <c r="O22" s="5" t="n"/>
+      <c r="P22" s="5" t="n"/>
+      <c r="Q22" s="5" t="n"/>
+      <c r="R22" s="5" t="n"/>
+      <c r="S22" s="5" t="n"/>
+      <c r="T22" s="5" t="n"/>
+      <c r="U22" s="5" t="n"/>
+      <c r="V22" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="W22" s="5" t="n"/>
+      <c r="X22" s="5" t="n"/>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="11">
+        <f>IF(C23="","",COUNTA(C18:C23))</f>
+        <v/>
+      </c>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>자원관리</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
+      <c r="I23" s="5" t="n"/>
+      <c r="J23" s="5" t="n"/>
+      <c r="K23" s="5" t="n"/>
+      <c r="L23" s="5" t="n"/>
+      <c r="M23" s="5" t="n"/>
+      <c r="N23" s="5" t="n"/>
+      <c r="O23" s="5" t="n"/>
+      <c r="P23" s="5" t="n"/>
+      <c r="Q23" s="5" t="n"/>
+      <c r="R23" s="5" t="n"/>
+      <c r="S23" s="5" t="n"/>
+      <c r="T23" s="5" t="n"/>
+      <c r="U23" s="5" t="n"/>
+      <c r="V23" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="W23" s="5" t="n"/>
+      <c r="X23" s="5" t="n"/>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="11">
+        <f>IF(C24="","",COUNTA(C18:C24))</f>
+        <v/>
+      </c>
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>설계관리</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="5" t="n"/>
+      <c r="I24" s="5" t="n"/>
+      <c r="J24" s="5" t="n"/>
+      <c r="K24" s="5" t="n"/>
+      <c r="L24" s="5" t="n"/>
+      <c r="M24" s="5" t="n"/>
+      <c r="N24" s="5" t="n"/>
+      <c r="O24" s="5" t="n"/>
+      <c r="P24" s="5" t="n"/>
+      <c r="Q24" s="5" t="n"/>
+      <c r="R24" s="5" t="n"/>
+      <c r="S24" s="5" t="n"/>
+      <c r="T24" s="5" t="n"/>
+      <c r="U24" s="5" t="n"/>
+      <c r="V24" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="W24" s="5" t="n"/>
+      <c r="X24" s="5" t="n"/>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="11">
+        <f>IF(C25="","",COUNTA(C18:C25))</f>
+        <v/>
+      </c>
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>건설공사 수행준비</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n"/>
+      <c r="I25" s="5" t="n"/>
+      <c r="J25" s="5" t="n"/>
+      <c r="K25" s="5" t="n"/>
+      <c r="L25" s="5" t="n"/>
+      <c r="M25" s="5" t="n"/>
+      <c r="N25" s="5" t="n"/>
+      <c r="O25" s="5" t="n"/>
+      <c r="P25" s="5" t="n"/>
+      <c r="Q25" s="5" t="n"/>
+      <c r="R25" s="5" t="n"/>
+      <c r="S25" s="5" t="n"/>
+      <c r="T25" s="5" t="n"/>
+      <c r="U25" s="5" t="n"/>
+      <c r="V25" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="W25" s="5" t="n"/>
+      <c r="X25" s="5" t="n"/>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="11">
+        <f>IF(C26="","",COUNTA(C18:C26))</f>
+        <v/>
+      </c>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>계약변경</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="5" t="n"/>
+      <c r="I26" s="5" t="n"/>
+      <c r="J26" s="5" t="n"/>
+      <c r="K26" s="5" t="n"/>
+      <c r="L26" s="5" t="n"/>
+      <c r="M26" s="5" t="n"/>
+      <c r="N26" s="5" t="n"/>
+      <c r="O26" s="5" t="n"/>
+      <c r="P26" s="5" t="n"/>
+      <c r="Q26" s="5" t="n"/>
+      <c r="R26" s="5" t="n"/>
+      <c r="S26" s="5" t="n"/>
+      <c r="T26" s="5" t="n"/>
+      <c r="U26" s="5" t="n"/>
+      <c r="V26" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="W26" s="5" t="n"/>
+      <c r="X26" s="5" t="n"/>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="11">
+        <f>IF(C27="","",COUNTA(C18:C27))</f>
+        <v/>
+      </c>
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>교육훈련</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="n"/>
+      <c r="I27" s="5" t="n"/>
+      <c r="J27" s="5" t="n"/>
+      <c r="K27" s="5" t="n"/>
+      <c r="L27" s="5" t="n"/>
+      <c r="M27" s="5" t="n"/>
+      <c r="N27" s="5" t="n"/>
+      <c r="O27" s="5" t="n"/>
+      <c r="P27" s="5" t="n"/>
+      <c r="Q27" s="5" t="n"/>
+      <c r="R27" s="5" t="n"/>
+      <c r="S27" s="5" t="n"/>
+      <c r="T27" s="5" t="n"/>
+      <c r="U27" s="5" t="n"/>
+      <c r="V27" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="W27" s="5" t="n"/>
+      <c r="X27" s="5" t="n"/>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="11">
+        <f>IF(C28="","",COUNTA(C18:C28))</f>
+        <v/>
+      </c>
+      <c r="B28" s="5" t="n"/>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>의사소통</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="5" t="n"/>
+      <c r="I28" s="5" t="n"/>
+      <c r="J28" s="5" t="n"/>
+      <c r="K28" s="5" t="n"/>
+      <c r="L28" s="5" t="n"/>
+      <c r="M28" s="5" t="n"/>
+      <c r="N28" s="5" t="n"/>
+      <c r="O28" s="5" t="n"/>
+      <c r="P28" s="5" t="n"/>
+      <c r="Q28" s="5" t="n"/>
+      <c r="R28" s="5" t="n"/>
+      <c r="S28" s="5" t="n"/>
+      <c r="T28" s="5" t="n"/>
+      <c r="U28" s="5" t="n"/>
+      <c r="V28" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="W28" s="5" t="n"/>
+      <c r="X28" s="5" t="n"/>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="11">
+        <f>IF(C29="","",COUNTA(C18:C29))</f>
+        <v/>
+      </c>
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>기자재 구매관리</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="5" t="n"/>
+      <c r="I29" s="5" t="n"/>
+      <c r="J29" s="5" t="n"/>
+      <c r="K29" s="5" t="n"/>
+      <c r="L29" s="5" t="n"/>
+      <c r="M29" s="5" t="n"/>
+      <c r="N29" s="5" t="n"/>
+      <c r="O29" s="5" t="n"/>
+      <c r="P29" s="5" t="n"/>
+      <c r="Q29" s="5" t="n"/>
+      <c r="R29" s="5" t="n"/>
+      <c r="S29" s="5" t="n"/>
+      <c r="T29" s="5" t="n"/>
+      <c r="U29" s="5" t="n"/>
+      <c r="V29" s="13" t="n">
+        <v>23</v>
+      </c>
+      <c r="W29" s="5" t="n"/>
+      <c r="X29" s="5" t="n"/>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="11">
+        <f>IF(C30="","",COUNTA(C18:C30))</f>
+        <v/>
+      </c>
+      <c r="B30" s="5" t="n"/>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>지급자재의 관리</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="5" t="n"/>
+      <c r="H30" s="5" t="n"/>
+      <c r="I30" s="5" t="n"/>
+      <c r="J30" s="5" t="n"/>
+      <c r="K30" s="5" t="n"/>
+      <c r="L30" s="5" t="n"/>
+      <c r="M30" s="5" t="n"/>
+      <c r="N30" s="5" t="n"/>
+      <c r="O30" s="5" t="n"/>
+      <c r="P30" s="5" t="n"/>
+      <c r="Q30" s="5" t="n"/>
+      <c r="R30" s="5" t="n"/>
+      <c r="S30" s="5" t="n"/>
+      <c r="T30" s="5" t="n"/>
+      <c r="U30" s="5" t="n"/>
+      <c r="V30" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="W30" s="5" t="n"/>
+      <c r="X30" s="5" t="n"/>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="11">
+        <f>IF(C31="","",COUNTA(C18:C31))</f>
+        <v/>
+      </c>
+      <c r="B31" s="5" t="n"/>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>하도급 관리</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="n"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5" t="n"/>
+      <c r="G31" s="5" t="n"/>
+      <c r="H31" s="5" t="n"/>
+      <c r="I31" s="5" t="n"/>
+      <c r="J31" s="5" t="n"/>
+      <c r="K31" s="5" t="n"/>
+      <c r="L31" s="5" t="n"/>
+      <c r="M31" s="5" t="n"/>
+      <c r="N31" s="5" t="n"/>
+      <c r="O31" s="5" t="n"/>
+      <c r="P31" s="5" t="n"/>
+      <c r="Q31" s="5" t="n"/>
+      <c r="R31" s="5" t="n"/>
+      <c r="S31" s="5" t="n"/>
+      <c r="T31" s="5" t="n"/>
+      <c r="U31" s="5" t="n"/>
+      <c r="V31" s="13" t="n">
+        <v>27</v>
+      </c>
+      <c r="W31" s="5" t="n"/>
+      <c r="X31" s="5" t="n"/>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="11">
+        <f>IF(C32="","",COUNTA(C18:C32))</f>
+        <v/>
+      </c>
+      <c r="B32" s="5" t="n"/>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>공사관리</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="n"/>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="5" t="n"/>
+      <c r="G32" s="5" t="n"/>
+      <c r="H32" s="5" t="n"/>
+      <c r="I32" s="5" t="n"/>
+      <c r="J32" s="5" t="n"/>
+      <c r="K32" s="5" t="n"/>
+      <c r="L32" s="5" t="n"/>
+      <c r="M32" s="5" t="n"/>
+      <c r="N32" s="5" t="n"/>
+      <c r="O32" s="5" t="n"/>
+      <c r="P32" s="5" t="n"/>
+      <c r="Q32" s="5" t="n"/>
+      <c r="R32" s="5" t="n"/>
+      <c r="S32" s="5" t="n"/>
+      <c r="T32" s="5" t="n"/>
+      <c r="U32" s="5" t="n"/>
+      <c r="V32" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="W32" s="5" t="n"/>
+      <c r="X32" s="5" t="n"/>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="11">
+        <f>IF(C33="","",COUNTA(C18:C33))</f>
+        <v/>
+      </c>
+      <c r="B33" s="5" t="n"/>
+      <c r="C33" s="12" t="inlineStr">
+        <is>
+          <t>중점 품질관리</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="n"/>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="5" t="n"/>
+      <c r="G33" s="5" t="n"/>
+      <c r="H33" s="5" t="n"/>
+      <c r="I33" s="5" t="n"/>
+      <c r="J33" s="5" t="n"/>
+      <c r="K33" s="5" t="n"/>
+      <c r="L33" s="5" t="n"/>
+      <c r="M33" s="5" t="n"/>
+      <c r="N33" s="5" t="n"/>
+      <c r="O33" s="5" t="n"/>
+      <c r="P33" s="5" t="n"/>
+      <c r="Q33" s="5" t="n"/>
+      <c r="R33" s="5" t="n"/>
+      <c r="S33" s="5" t="n"/>
+      <c r="T33" s="5" t="n"/>
+      <c r="U33" s="5" t="n"/>
+      <c r="V33" s="13" t="n">
+        <v>34</v>
+      </c>
+      <c r="W33" s="5" t="n"/>
+      <c r="X33" s="5" t="n"/>
+    </row>
+    <row r="34" ht="6" customHeight="1"/>
+    <row r="35" ht="10" customHeight="1"/>
+    <row r="36" ht="26" customHeight="1">
+      <c r="A36" s="14" t="n">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="15" t="inlineStr"/>
+      <c r="K37" s="16" t="inlineStr">
+        <is>
+          <t>품질관리자</t>
+        </is>
+      </c>
+      <c r="Q37" s="17" t="inlineStr">
+        <is>
+          <t>한품질</t>
+        </is>
+      </c>
+      <c r="U37" s="18" t="inlineStr">
+        <is>
+          <t>(서명 또는 인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="15" t="inlineStr"/>
+      <c r="K38" s="16" t="inlineStr">
+        <is>
+          <t>현장대리인</t>
+        </is>
+      </c>
+      <c r="Q38" s="17" t="inlineStr">
+        <is>
+          <t>김철수</t>
+        </is>
+      </c>
+      <c r="U38" s="18" t="inlineStr">
+        <is>
+          <t>(서명 또는 인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="6" customHeight="1"/>
+    <row r="41" ht="19.5" customHeight="1">
+      <c r="A41" s="19" t="inlineStr">
+        <is>
+          <t>이 시트는 작성 예시입니다(가상의 현장 · 이름 · 금액). 실제로는 앞 시트에 적으세요.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="81">
+    <mergeCell ref="V24:X24"/>
+    <mergeCell ref="C23:U23"/>
+    <mergeCell ref="U38:X38"/>
+    <mergeCell ref="A3:X3"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="C18:U18"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="K38:P38"/>
+    <mergeCell ref="V22:X22"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="V21:X21"/>
+    <mergeCell ref="C20:U20"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="G12:X12"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="V23:X23"/>
+    <mergeCell ref="C22:U22"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="G7:X7"/>
+    <mergeCell ref="A38:J38"/>
+    <mergeCell ref="C32:U32"/>
+    <mergeCell ref="V27:X27"/>
+    <mergeCell ref="Q37:T37"/>
+    <mergeCell ref="V25:X25"/>
+    <mergeCell ref="C24:U24"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C33:U33"/>
+    <mergeCell ref="K37:P37"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="C26:U26"/>
+    <mergeCell ref="G9:X9"/>
+    <mergeCell ref="V17:X17"/>
+    <mergeCell ref="Q38:T38"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="C25:U25"/>
+    <mergeCell ref="G11:X11"/>
+    <mergeCell ref="A15:X15"/>
+    <mergeCell ref="V20:X20"/>
+    <mergeCell ref="V29:X29"/>
+    <mergeCell ref="V31:X31"/>
+    <mergeCell ref="A41:X41"/>
+    <mergeCell ref="G13:X13"/>
+    <mergeCell ref="V32:X32"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="V26:X26"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="V18:X18"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="V33:X33"/>
+    <mergeCell ref="U37:X37"/>
+    <mergeCell ref="V19:X19"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="V28:X28"/>
+    <mergeCell ref="C27:U27"/>
     <mergeCell ref="C17:U17"/>
     <mergeCell ref="G6:X6"/>
     <mergeCell ref="A12:F12"/>
@@ -1366,6 +2568,7 @@
     <mergeCell ref="C30:U30"/>
     <mergeCell ref="C29:U29"/>
     <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A37:J37"/>
     <mergeCell ref="A29:B29"/>
     <mergeCell ref="C31:U31"/>
     <mergeCell ref="A1:L1"/>
@@ -1376,7 +2579,8 @@
     <mergeCell ref="A31:B31"/>
     <mergeCell ref="G8:X8"/>
   </mergeCells>
-  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/web/public/forms/pumjil-gwanri-gyehoek.xlsx
+++ b/web/public/forms/pumjil-gwanri-gyehoek.xlsx
@@ -590,7 +590,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
@@ -1550,7 +1550,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="M1" s="20" t="inlineStr">

--- a/web/public/forms/pumjil-gwanri-gyehoek.xlsx
+++ b/web/public/forms/pumjil-gwanri-gyehoek.xlsx
@@ -8,11 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="품질관리계획서 표지·목차" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성 예시" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'품질관리계획서 표지·목차'!$A$1:$X$39</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'작성 예시'!$A$1:$X$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -133,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -189,9 +187,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -897,10 +892,7 @@
       <c r="X17" s="5" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="11">
-        <f>IF(C18="","",COUNTA(C18:C18))</f>
-        <v/>
-      </c>
+      <c r="A18" s="11" t="n"/>
       <c r="B18" s="5" t="n"/>
       <c r="C18" s="12" t="n"/>
       <c r="D18" s="5" t="n"/>
@@ -926,10 +918,7 @@
       <c r="X18" s="5" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="11">
-        <f>IF(C19="","",COUNTA(C18:C19))</f>
-        <v/>
-      </c>
+      <c r="A19" s="11" t="n"/>
       <c r="B19" s="5" t="n"/>
       <c r="C19" s="12" t="n"/>
       <c r="D19" s="5" t="n"/>
@@ -955,10 +944,7 @@
       <c r="X19" s="5" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="11">
-        <f>IF(C20="","",COUNTA(C18:C20))</f>
-        <v/>
-      </c>
+      <c r="A20" s="11" t="n"/>
       <c r="B20" s="5" t="n"/>
       <c r="C20" s="12" t="n"/>
       <c r="D20" s="5" t="n"/>
@@ -984,10 +970,7 @@
       <c r="X20" s="5" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="11">
-        <f>IF(C21="","",COUNTA(C18:C21))</f>
-        <v/>
-      </c>
+      <c r="A21" s="11" t="n"/>
       <c r="B21" s="5" t="n"/>
       <c r="C21" s="12" t="n"/>
       <c r="D21" s="5" t="n"/>
@@ -1013,10 +996,7 @@
       <c r="X21" s="5" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="11">
-        <f>IF(C22="","",COUNTA(C18:C22))</f>
-        <v/>
-      </c>
+      <c r="A22" s="11" t="n"/>
       <c r="B22" s="5" t="n"/>
       <c r="C22" s="12" t="n"/>
       <c r="D22" s="5" t="n"/>
@@ -1042,10 +1022,7 @@
       <c r="X22" s="5" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="11">
-        <f>IF(C23="","",COUNTA(C18:C23))</f>
-        <v/>
-      </c>
+      <c r="A23" s="11" t="n"/>
       <c r="B23" s="5" t="n"/>
       <c r="C23" s="12" t="n"/>
       <c r="D23" s="5" t="n"/>
@@ -1071,10 +1048,7 @@
       <c r="X23" s="5" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="11">
-        <f>IF(C24="","",COUNTA(C18:C24))</f>
-        <v/>
-      </c>
+      <c r="A24" s="11" t="n"/>
       <c r="B24" s="5" t="n"/>
       <c r="C24" s="12" t="n"/>
       <c r="D24" s="5" t="n"/>
@@ -1100,10 +1074,7 @@
       <c r="X24" s="5" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="11">
-        <f>IF(C25="","",COUNTA(C18:C25))</f>
-        <v/>
-      </c>
+      <c r="A25" s="11" t="n"/>
       <c r="B25" s="5" t="n"/>
       <c r="C25" s="12" t="n"/>
       <c r="D25" s="5" t="n"/>
@@ -1129,10 +1100,7 @@
       <c r="X25" s="5" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="11">
-        <f>IF(C26="","",COUNTA(C18:C26))</f>
-        <v/>
-      </c>
+      <c r="A26" s="11" t="n"/>
       <c r="B26" s="5" t="n"/>
       <c r="C26" s="12" t="n"/>
       <c r="D26" s="5" t="n"/>
@@ -1158,10 +1126,7 @@
       <c r="X26" s="5" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="11">
-        <f>IF(C27="","",COUNTA(C18:C27))</f>
-        <v/>
-      </c>
+      <c r="A27" s="11" t="n"/>
       <c r="B27" s="5" t="n"/>
       <c r="C27" s="12" t="n"/>
       <c r="D27" s="5" t="n"/>
@@ -1187,10 +1152,7 @@
       <c r="X27" s="5" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="11">
-        <f>IF(C28="","",COUNTA(C18:C28))</f>
-        <v/>
-      </c>
+      <c r="A28" s="11" t="n"/>
       <c r="B28" s="5" t="n"/>
       <c r="C28" s="12" t="n"/>
       <c r="D28" s="5" t="n"/>
@@ -1216,10 +1178,7 @@
       <c r="X28" s="5" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="11">
-        <f>IF(C29="","",COUNTA(C18:C29))</f>
-        <v/>
-      </c>
+      <c r="A29" s="11" t="n"/>
       <c r="B29" s="5" t="n"/>
       <c r="C29" s="12" t="n"/>
       <c r="D29" s="5" t="n"/>
@@ -1245,10 +1204,7 @@
       <c r="X29" s="5" t="n"/>
     </row>
     <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="11">
-        <f>IF(C30="","",COUNTA(C18:C30))</f>
-        <v/>
-      </c>
+      <c r="A30" s="11" t="n"/>
       <c r="B30" s="5" t="n"/>
       <c r="C30" s="12" t="n"/>
       <c r="D30" s="5" t="n"/>
@@ -1274,10 +1230,7 @@
       <c r="X30" s="5" t="n"/>
     </row>
     <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="11">
-        <f>IF(C31="","",COUNTA(C18:C31))</f>
-        <v/>
-      </c>
+      <c r="A31" s="11" t="n"/>
       <c r="B31" s="5" t="n"/>
       <c r="C31" s="12" t="n"/>
       <c r="D31" s="5" t="n"/>
@@ -1303,10 +1256,7 @@
       <c r="X31" s="5" t="n"/>
     </row>
     <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="11">
-        <f>IF(C32="","",COUNTA(C18:C32))</f>
-        <v/>
-      </c>
+      <c r="A32" s="11" t="n"/>
       <c r="B32" s="5" t="n"/>
       <c r="C32" s="12" t="n"/>
       <c r="D32" s="5" t="n"/>
@@ -1332,10 +1282,7 @@
       <c r="X32" s="5" t="n"/>
     </row>
     <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="11">
-        <f>IF(C33="","",COUNTA(C18:C33))</f>
-        <v/>
-      </c>
+      <c r="A33" s="11" t="n"/>
       <c r="B33" s="5" t="n"/>
       <c r="C33" s="12" t="n"/>
       <c r="D33" s="5" t="n"/>
@@ -1398,6 +1345,7 @@
       </c>
     </row>
     <row r="39" ht="6" customHeight="1"/>
+    <row r="40"/>
     <row r="41" ht="34" customHeight="1">
       <c r="A41" s="19" t="inlineStr">
         <is>
@@ -1509,1078 +1457,4 @@
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00F59E0B"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:X41"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="3.6" customWidth="1" min="1" max="1"/>
-    <col width="3.6" customWidth="1" min="2" max="2"/>
-    <col width="3.6" customWidth="1" min="3" max="3"/>
-    <col width="3.6" customWidth="1" min="4" max="4"/>
-    <col width="3.6" customWidth="1" min="5" max="5"/>
-    <col width="3.6" customWidth="1" min="6" max="6"/>
-    <col width="3.6" customWidth="1" min="7" max="7"/>
-    <col width="3.6" customWidth="1" min="8" max="8"/>
-    <col width="3.6" customWidth="1" min="9" max="9"/>
-    <col width="3.6" customWidth="1" min="10" max="10"/>
-    <col width="3.6" customWidth="1" min="11" max="11"/>
-    <col width="3.6" customWidth="1" min="12" max="12"/>
-    <col width="3.6" customWidth="1" min="13" max="13"/>
-    <col width="3.6" customWidth="1" min="14" max="14"/>
-    <col width="3.6" customWidth="1" min="15" max="15"/>
-    <col width="3.6" customWidth="1" min="16" max="16"/>
-    <col width="3.6" customWidth="1" min="17" max="17"/>
-    <col width="3.6" customWidth="1" min="18" max="18"/>
-    <col width="3.6" customWidth="1" min="19" max="19"/>
-    <col width="3.6" customWidth="1" min="20" max="20"/>
-    <col width="3.6" customWidth="1" min="21" max="21"/>
-    <col width="3.6" customWidth="1" min="22" max="22"/>
-    <col width="3.6" customWidth="1" min="23" max="23"/>
-    <col width="3.6" customWidth="1" min="24" max="24"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
-        </is>
-      </c>
-      <c r="M1" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="6" customHeight="1"/>
-    <row r="3" ht="38" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>품 질 관 리 계 획 서</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="10" customHeight="1"/>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  공 사 명</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>가나지구 배수로 정비공사</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="5" t="n"/>
-      <c r="K5" s="5" t="n"/>
-      <c r="L5" s="5" t="n"/>
-      <c r="M5" s="5" t="n"/>
-      <c r="N5" s="5" t="n"/>
-      <c r="O5" s="5" t="n"/>
-      <c r="P5" s="5" t="n"/>
-      <c r="Q5" s="5" t="n"/>
-      <c r="R5" s="5" t="n"/>
-      <c r="S5" s="5" t="n"/>
-      <c r="T5" s="5" t="n"/>
-      <c r="U5" s="5" t="n"/>
-      <c r="V5" s="5" t="n"/>
-      <c r="W5" s="5" t="n"/>
-      <c r="X5" s="5" t="n"/>
-    </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  발 주 기 관</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>가나시 건설과</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="n"/>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="5" t="n"/>
-      <c r="K6" s="5" t="n"/>
-      <c r="L6" s="5" t="n"/>
-      <c r="M6" s="5" t="n"/>
-      <c r="N6" s="5" t="n"/>
-      <c r="O6" s="5" t="n"/>
-      <c r="P6" s="5" t="n"/>
-      <c r="Q6" s="5" t="n"/>
-      <c r="R6" s="5" t="n"/>
-      <c r="S6" s="5" t="n"/>
-      <c r="T6" s="5" t="n"/>
-      <c r="U6" s="5" t="n"/>
-      <c r="V6" s="5" t="n"/>
-      <c r="W6" s="5" t="n"/>
-      <c r="X6" s="5" t="n"/>
-    </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  계 약 금 액</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="7" t="n">
-        <v>963241000</v>
-      </c>
-      <c r="H7" s="5" t="n"/>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="5" t="n"/>
-      <c r="K7" s="5" t="n"/>
-      <c r="L7" s="5" t="n"/>
-      <c r="M7" s="5" t="n"/>
-      <c r="N7" s="5" t="n"/>
-      <c r="O7" s="5" t="n"/>
-      <c r="P7" s="5" t="n"/>
-      <c r="Q7" s="5" t="n"/>
-      <c r="R7" s="5" t="n"/>
-      <c r="S7" s="5" t="n"/>
-      <c r="T7" s="5" t="n"/>
-      <c r="U7" s="5" t="n"/>
-      <c r="V7" s="5" t="n"/>
-      <c r="W7" s="5" t="n"/>
-      <c r="X7" s="5" t="n"/>
-    </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  공        기</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>2026. 3. 9. ~ 2026. 12. 31. (298일)</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="n"/>
-      <c r="K8" s="5" t="n"/>
-      <c r="L8" s="5" t="n"/>
-      <c r="M8" s="5" t="n"/>
-      <c r="N8" s="5" t="n"/>
-      <c r="O8" s="5" t="n"/>
-      <c r="P8" s="5" t="n"/>
-      <c r="Q8" s="5" t="n"/>
-      <c r="R8" s="5" t="n"/>
-      <c r="S8" s="5" t="n"/>
-      <c r="T8" s="5" t="n"/>
-      <c r="U8" s="5" t="n"/>
-      <c r="V8" s="5" t="n"/>
-      <c r="W8" s="5" t="n"/>
-      <c r="X8" s="5" t="n"/>
-    </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  작 성 일 자</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="8" t="n">
-        <v>46294</v>
-      </c>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="5" t="n"/>
-      <c r="K9" s="5" t="n"/>
-      <c r="L9" s="5" t="n"/>
-      <c r="M9" s="5" t="n"/>
-      <c r="N9" s="5" t="n"/>
-      <c r="O9" s="5" t="n"/>
-      <c r="P9" s="5" t="n"/>
-      <c r="Q9" s="5" t="n"/>
-      <c r="R9" s="5" t="n"/>
-      <c r="S9" s="5" t="n"/>
-      <c r="T9" s="5" t="n"/>
-      <c r="U9" s="5" t="n"/>
-      <c r="V9" s="5" t="n"/>
-      <c r="W9" s="5" t="n"/>
-      <c r="X9" s="5" t="n"/>
-    </row>
-    <row r="10" ht="6" customHeight="1"/>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  작 성 부 서</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>예시건설(주) 가나지구 현장</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="n"/>
-      <c r="I11" s="5" t="n"/>
-      <c r="J11" s="5" t="n"/>
-      <c r="K11" s="5" t="n"/>
-      <c r="L11" s="5" t="n"/>
-      <c r="M11" s="5" t="n"/>
-      <c r="N11" s="5" t="n"/>
-      <c r="O11" s="5" t="n"/>
-      <c r="P11" s="5" t="n"/>
-      <c r="Q11" s="5" t="n"/>
-      <c r="R11" s="5" t="n"/>
-      <c r="S11" s="5" t="n"/>
-      <c r="T11" s="5" t="n"/>
-      <c r="U11" s="5" t="n"/>
-      <c r="V11" s="5" t="n"/>
-      <c r="W11" s="5" t="n"/>
-      <c r="X11" s="5" t="n"/>
-    </row>
-    <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  품질관리자</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>한품질(건설재료시험기사)</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="n"/>
-      <c r="I12" s="5" t="n"/>
-      <c r="J12" s="5" t="n"/>
-      <c r="K12" s="5" t="n"/>
-      <c r="L12" s="5" t="n"/>
-      <c r="M12" s="5" t="n"/>
-      <c r="N12" s="5" t="n"/>
-      <c r="O12" s="5" t="n"/>
-      <c r="P12" s="5" t="n"/>
-      <c r="Q12" s="5" t="n"/>
-      <c r="R12" s="5" t="n"/>
-      <c r="S12" s="5" t="n"/>
-      <c r="T12" s="5" t="n"/>
-      <c r="U12" s="5" t="n"/>
-      <c r="V12" s="5" t="n"/>
-      <c r="W12" s="5" t="n"/>
-      <c r="X12" s="5" t="n"/>
-    </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  검토·승인 이력</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>2026. 3. 16. 제출 → 3. 23. 감리 승인</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="n"/>
-      <c r="I13" s="5" t="n"/>
-      <c r="J13" s="5" t="n"/>
-      <c r="K13" s="5" t="n"/>
-      <c r="L13" s="5" t="n"/>
-      <c r="M13" s="5" t="n"/>
-      <c r="N13" s="5" t="n"/>
-      <c r="O13" s="5" t="n"/>
-      <c r="P13" s="5" t="n"/>
-      <c r="Q13" s="5" t="n"/>
-      <c r="R13" s="5" t="n"/>
-      <c r="S13" s="5" t="n"/>
-      <c r="T13" s="5" t="n"/>
-      <c r="U13" s="5" t="n"/>
-      <c r="V13" s="5" t="n"/>
-      <c r="W13" s="5" t="n"/>
-      <c r="X13" s="5" t="n"/>
-    </row>
-    <row r="14" ht="6" customHeight="1"/>
-    <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>■ 목  차</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="6" customHeight="1"/>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>장</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>제        목</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="5" t="n"/>
-      <c r="I17" s="5" t="n"/>
-      <c r="J17" s="5" t="n"/>
-      <c r="K17" s="5" t="n"/>
-      <c r="L17" s="5" t="n"/>
-      <c r="M17" s="5" t="n"/>
-      <c r="N17" s="5" t="n"/>
-      <c r="O17" s="5" t="n"/>
-      <c r="P17" s="5" t="n"/>
-      <c r="Q17" s="5" t="n"/>
-      <c r="R17" s="5" t="n"/>
-      <c r="S17" s="5" t="n"/>
-      <c r="T17" s="5" t="n"/>
-      <c r="U17" s="5" t="n"/>
-      <c r="V17" s="10" t="inlineStr">
-        <is>
-          <t>면</t>
-        </is>
-      </c>
-      <c r="W17" s="5" t="n"/>
-      <c r="X17" s="5" t="n"/>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="11">
-        <f>IF(C18="","",COUNTA(C18:C18))</f>
-        <v/>
-      </c>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="12" t="inlineStr">
-        <is>
-          <t>건설공사 정보</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n"/>
-      <c r="I18" s="5" t="n"/>
-      <c r="J18" s="5" t="n"/>
-      <c r="K18" s="5" t="n"/>
-      <c r="L18" s="5" t="n"/>
-      <c r="M18" s="5" t="n"/>
-      <c r="N18" s="5" t="n"/>
-      <c r="O18" s="5" t="n"/>
-      <c r="P18" s="5" t="n"/>
-      <c r="Q18" s="5" t="n"/>
-      <c r="R18" s="5" t="n"/>
-      <c r="S18" s="5" t="n"/>
-      <c r="T18" s="5" t="n"/>
-      <c r="U18" s="5" t="n"/>
-      <c r="V18" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="W18" s="5" t="n"/>
-      <c r="X18" s="5" t="n"/>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="11">
-        <f>IF(C19="","",COUNTA(C18:C19))</f>
-        <v/>
-      </c>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="12" t="inlineStr">
-        <is>
-          <t>현장 품질방침 및 품질목표</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="5" t="n"/>
-      <c r="I19" s="5" t="n"/>
-      <c r="J19" s="5" t="n"/>
-      <c r="K19" s="5" t="n"/>
-      <c r="L19" s="5" t="n"/>
-      <c r="M19" s="5" t="n"/>
-      <c r="N19" s="5" t="n"/>
-      <c r="O19" s="5" t="n"/>
-      <c r="P19" s="5" t="n"/>
-      <c r="Q19" s="5" t="n"/>
-      <c r="R19" s="5" t="n"/>
-      <c r="S19" s="5" t="n"/>
-      <c r="T19" s="5" t="n"/>
-      <c r="U19" s="5" t="n"/>
-      <c r="V19" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="W19" s="5" t="n"/>
-      <c r="X19" s="5" t="n"/>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="11">
-        <f>IF(C20="","",COUNTA(C18:C20))</f>
-        <v/>
-      </c>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="12" t="inlineStr">
-        <is>
-          <t>책임 및 권한</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="n"/>
-      <c r="I20" s="5" t="n"/>
-      <c r="J20" s="5" t="n"/>
-      <c r="K20" s="5" t="n"/>
-      <c r="L20" s="5" t="n"/>
-      <c r="M20" s="5" t="n"/>
-      <c r="N20" s="5" t="n"/>
-      <c r="O20" s="5" t="n"/>
-      <c r="P20" s="5" t="n"/>
-      <c r="Q20" s="5" t="n"/>
-      <c r="R20" s="5" t="n"/>
-      <c r="S20" s="5" t="n"/>
-      <c r="T20" s="5" t="n"/>
-      <c r="U20" s="5" t="n"/>
-      <c r="V20" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="W20" s="5" t="n"/>
-      <c r="X20" s="5" t="n"/>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="11">
-        <f>IF(C21="","",COUNTA(C18:C21))</f>
-        <v/>
-      </c>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="12" t="inlineStr">
-        <is>
-          <t>문서관리</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="5" t="n"/>
-      <c r="I21" s="5" t="n"/>
-      <c r="J21" s="5" t="n"/>
-      <c r="K21" s="5" t="n"/>
-      <c r="L21" s="5" t="n"/>
-      <c r="M21" s="5" t="n"/>
-      <c r="N21" s="5" t="n"/>
-      <c r="O21" s="5" t="n"/>
-      <c r="P21" s="5" t="n"/>
-      <c r="Q21" s="5" t="n"/>
-      <c r="R21" s="5" t="n"/>
-      <c r="S21" s="5" t="n"/>
-      <c r="T21" s="5" t="n"/>
-      <c r="U21" s="5" t="n"/>
-      <c r="V21" s="13" t="n">
-        <v>7</v>
-      </c>
-      <c r="W21" s="5" t="n"/>
-      <c r="X21" s="5" t="n"/>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="11">
-        <f>IF(C22="","",COUNTA(C18:C22))</f>
-        <v/>
-      </c>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="12" t="inlineStr">
-        <is>
-          <t>기록관리</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n"/>
-      <c r="I22" s="5" t="n"/>
-      <c r="J22" s="5" t="n"/>
-      <c r="K22" s="5" t="n"/>
-      <c r="L22" s="5" t="n"/>
-      <c r="M22" s="5" t="n"/>
-      <c r="N22" s="5" t="n"/>
-      <c r="O22" s="5" t="n"/>
-      <c r="P22" s="5" t="n"/>
-      <c r="Q22" s="5" t="n"/>
-      <c r="R22" s="5" t="n"/>
-      <c r="S22" s="5" t="n"/>
-      <c r="T22" s="5" t="n"/>
-      <c r="U22" s="5" t="n"/>
-      <c r="V22" s="13" t="n">
-        <v>9</v>
-      </c>
-      <c r="W22" s="5" t="n"/>
-      <c r="X22" s="5" t="n"/>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="11">
-        <f>IF(C23="","",COUNTA(C18:C23))</f>
-        <v/>
-      </c>
-      <c r="B23" s="5" t="n"/>
-      <c r="C23" s="12" t="inlineStr">
-        <is>
-          <t>자원관리</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="5" t="n"/>
-      <c r="H23" s="5" t="n"/>
-      <c r="I23" s="5" t="n"/>
-      <c r="J23" s="5" t="n"/>
-      <c r="K23" s="5" t="n"/>
-      <c r="L23" s="5" t="n"/>
-      <c r="M23" s="5" t="n"/>
-      <c r="N23" s="5" t="n"/>
-      <c r="O23" s="5" t="n"/>
-      <c r="P23" s="5" t="n"/>
-      <c r="Q23" s="5" t="n"/>
-      <c r="R23" s="5" t="n"/>
-      <c r="S23" s="5" t="n"/>
-      <c r="T23" s="5" t="n"/>
-      <c r="U23" s="5" t="n"/>
-      <c r="V23" s="13" t="n">
-        <v>11</v>
-      </c>
-      <c r="W23" s="5" t="n"/>
-      <c r="X23" s="5" t="n"/>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="11">
-        <f>IF(C24="","",COUNTA(C18:C24))</f>
-        <v/>
-      </c>
-      <c r="B24" s="5" t="n"/>
-      <c r="C24" s="12" t="inlineStr">
-        <is>
-          <t>설계관리</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="n"/>
-      <c r="G24" s="5" t="n"/>
-      <c r="H24" s="5" t="n"/>
-      <c r="I24" s="5" t="n"/>
-      <c r="J24" s="5" t="n"/>
-      <c r="K24" s="5" t="n"/>
-      <c r="L24" s="5" t="n"/>
-      <c r="M24" s="5" t="n"/>
-      <c r="N24" s="5" t="n"/>
-      <c r="O24" s="5" t="n"/>
-      <c r="P24" s="5" t="n"/>
-      <c r="Q24" s="5" t="n"/>
-      <c r="R24" s="5" t="n"/>
-      <c r="S24" s="5" t="n"/>
-      <c r="T24" s="5" t="n"/>
-      <c r="U24" s="5" t="n"/>
-      <c r="V24" s="13" t="n">
-        <v>13</v>
-      </c>
-      <c r="W24" s="5" t="n"/>
-      <c r="X24" s="5" t="n"/>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="11">
-        <f>IF(C25="","",COUNTA(C18:C25))</f>
-        <v/>
-      </c>
-      <c r="B25" s="5" t="n"/>
-      <c r="C25" s="12" t="inlineStr">
-        <is>
-          <t>건설공사 수행준비</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="n"/>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5" t="n"/>
-      <c r="G25" s="5" t="n"/>
-      <c r="H25" s="5" t="n"/>
-      <c r="I25" s="5" t="n"/>
-      <c r="J25" s="5" t="n"/>
-      <c r="K25" s="5" t="n"/>
-      <c r="L25" s="5" t="n"/>
-      <c r="M25" s="5" t="n"/>
-      <c r="N25" s="5" t="n"/>
-      <c r="O25" s="5" t="n"/>
-      <c r="P25" s="5" t="n"/>
-      <c r="Q25" s="5" t="n"/>
-      <c r="R25" s="5" t="n"/>
-      <c r="S25" s="5" t="n"/>
-      <c r="T25" s="5" t="n"/>
-      <c r="U25" s="5" t="n"/>
-      <c r="V25" s="13" t="n">
-        <v>15</v>
-      </c>
-      <c r="W25" s="5" t="n"/>
-      <c r="X25" s="5" t="n"/>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="11">
-        <f>IF(C26="","",COUNTA(C18:C26))</f>
-        <v/>
-      </c>
-      <c r="B26" s="5" t="n"/>
-      <c r="C26" s="12" t="inlineStr">
-        <is>
-          <t>계약변경</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5" t="n"/>
-      <c r="G26" s="5" t="n"/>
-      <c r="H26" s="5" t="n"/>
-      <c r="I26" s="5" t="n"/>
-      <c r="J26" s="5" t="n"/>
-      <c r="K26" s="5" t="n"/>
-      <c r="L26" s="5" t="n"/>
-      <c r="M26" s="5" t="n"/>
-      <c r="N26" s="5" t="n"/>
-      <c r="O26" s="5" t="n"/>
-      <c r="P26" s="5" t="n"/>
-      <c r="Q26" s="5" t="n"/>
-      <c r="R26" s="5" t="n"/>
-      <c r="S26" s="5" t="n"/>
-      <c r="T26" s="5" t="n"/>
-      <c r="U26" s="5" t="n"/>
-      <c r="V26" s="13" t="n">
-        <v>17</v>
-      </c>
-      <c r="W26" s="5" t="n"/>
-      <c r="X26" s="5" t="n"/>
-    </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="11">
-        <f>IF(C27="","",COUNTA(C18:C27))</f>
-        <v/>
-      </c>
-      <c r="B27" s="5" t="n"/>
-      <c r="C27" s="12" t="inlineStr">
-        <is>
-          <t>교육훈련</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="5" t="n"/>
-      <c r="G27" s="5" t="n"/>
-      <c r="H27" s="5" t="n"/>
-      <c r="I27" s="5" t="n"/>
-      <c r="J27" s="5" t="n"/>
-      <c r="K27" s="5" t="n"/>
-      <c r="L27" s="5" t="n"/>
-      <c r="M27" s="5" t="n"/>
-      <c r="N27" s="5" t="n"/>
-      <c r="O27" s="5" t="n"/>
-      <c r="P27" s="5" t="n"/>
-      <c r="Q27" s="5" t="n"/>
-      <c r="R27" s="5" t="n"/>
-      <c r="S27" s="5" t="n"/>
-      <c r="T27" s="5" t="n"/>
-      <c r="U27" s="5" t="n"/>
-      <c r="V27" s="13" t="n">
-        <v>19</v>
-      </c>
-      <c r="W27" s="5" t="n"/>
-      <c r="X27" s="5" t="n"/>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="11">
-        <f>IF(C28="","",COUNTA(C18:C28))</f>
-        <v/>
-      </c>
-      <c r="B28" s="5" t="n"/>
-      <c r="C28" s="12" t="inlineStr">
-        <is>
-          <t>의사소통</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="5" t="n"/>
-      <c r="F28" s="5" t="n"/>
-      <c r="G28" s="5" t="n"/>
-      <c r="H28" s="5" t="n"/>
-      <c r="I28" s="5" t="n"/>
-      <c r="J28" s="5" t="n"/>
-      <c r="K28" s="5" t="n"/>
-      <c r="L28" s="5" t="n"/>
-      <c r="M28" s="5" t="n"/>
-      <c r="N28" s="5" t="n"/>
-      <c r="O28" s="5" t="n"/>
-      <c r="P28" s="5" t="n"/>
-      <c r="Q28" s="5" t="n"/>
-      <c r="R28" s="5" t="n"/>
-      <c r="S28" s="5" t="n"/>
-      <c r="T28" s="5" t="n"/>
-      <c r="U28" s="5" t="n"/>
-      <c r="V28" s="13" t="n">
-        <v>21</v>
-      </c>
-      <c r="W28" s="5" t="n"/>
-      <c r="X28" s="5" t="n"/>
-    </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="11">
-        <f>IF(C29="","",COUNTA(C18:C29))</f>
-        <v/>
-      </c>
-      <c r="B29" s="5" t="n"/>
-      <c r="C29" s="12" t="inlineStr">
-        <is>
-          <t>기자재 구매관리</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="n"/>
-      <c r="E29" s="5" t="n"/>
-      <c r="F29" s="5" t="n"/>
-      <c r="G29" s="5" t="n"/>
-      <c r="H29" s="5" t="n"/>
-      <c r="I29" s="5" t="n"/>
-      <c r="J29" s="5" t="n"/>
-      <c r="K29" s="5" t="n"/>
-      <c r="L29" s="5" t="n"/>
-      <c r="M29" s="5" t="n"/>
-      <c r="N29" s="5" t="n"/>
-      <c r="O29" s="5" t="n"/>
-      <c r="P29" s="5" t="n"/>
-      <c r="Q29" s="5" t="n"/>
-      <c r="R29" s="5" t="n"/>
-      <c r="S29" s="5" t="n"/>
-      <c r="T29" s="5" t="n"/>
-      <c r="U29" s="5" t="n"/>
-      <c r="V29" s="13" t="n">
-        <v>23</v>
-      </c>
-      <c r="W29" s="5" t="n"/>
-      <c r="X29" s="5" t="n"/>
-    </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="11">
-        <f>IF(C30="","",COUNTA(C18:C30))</f>
-        <v/>
-      </c>
-      <c r="B30" s="5" t="n"/>
-      <c r="C30" s="12" t="inlineStr">
-        <is>
-          <t>지급자재의 관리</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="5" t="n"/>
-      <c r="F30" s="5" t="n"/>
-      <c r="G30" s="5" t="n"/>
-      <c r="H30" s="5" t="n"/>
-      <c r="I30" s="5" t="n"/>
-      <c r="J30" s="5" t="n"/>
-      <c r="K30" s="5" t="n"/>
-      <c r="L30" s="5" t="n"/>
-      <c r="M30" s="5" t="n"/>
-      <c r="N30" s="5" t="n"/>
-      <c r="O30" s="5" t="n"/>
-      <c r="P30" s="5" t="n"/>
-      <c r="Q30" s="5" t="n"/>
-      <c r="R30" s="5" t="n"/>
-      <c r="S30" s="5" t="n"/>
-      <c r="T30" s="5" t="n"/>
-      <c r="U30" s="5" t="n"/>
-      <c r="V30" s="13" t="n">
-        <v>25</v>
-      </c>
-      <c r="W30" s="5" t="n"/>
-      <c r="X30" s="5" t="n"/>
-    </row>
-    <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="11">
-        <f>IF(C31="","",COUNTA(C18:C31))</f>
-        <v/>
-      </c>
-      <c r="B31" s="5" t="n"/>
-      <c r="C31" s="12" t="inlineStr">
-        <is>
-          <t>하도급 관리</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="n"/>
-      <c r="E31" s="5" t="n"/>
-      <c r="F31" s="5" t="n"/>
-      <c r="G31" s="5" t="n"/>
-      <c r="H31" s="5" t="n"/>
-      <c r="I31" s="5" t="n"/>
-      <c r="J31" s="5" t="n"/>
-      <c r="K31" s="5" t="n"/>
-      <c r="L31" s="5" t="n"/>
-      <c r="M31" s="5" t="n"/>
-      <c r="N31" s="5" t="n"/>
-      <c r="O31" s="5" t="n"/>
-      <c r="P31" s="5" t="n"/>
-      <c r="Q31" s="5" t="n"/>
-      <c r="R31" s="5" t="n"/>
-      <c r="S31" s="5" t="n"/>
-      <c r="T31" s="5" t="n"/>
-      <c r="U31" s="5" t="n"/>
-      <c r="V31" s="13" t="n">
-        <v>27</v>
-      </c>
-      <c r="W31" s="5" t="n"/>
-      <c r="X31" s="5" t="n"/>
-    </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="11">
-        <f>IF(C32="","",COUNTA(C18:C32))</f>
-        <v/>
-      </c>
-      <c r="B32" s="5" t="n"/>
-      <c r="C32" s="12" t="inlineStr">
-        <is>
-          <t>공사관리</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="n"/>
-      <c r="E32" s="5" t="n"/>
-      <c r="F32" s="5" t="n"/>
-      <c r="G32" s="5" t="n"/>
-      <c r="H32" s="5" t="n"/>
-      <c r="I32" s="5" t="n"/>
-      <c r="J32" s="5" t="n"/>
-      <c r="K32" s="5" t="n"/>
-      <c r="L32" s="5" t="n"/>
-      <c r="M32" s="5" t="n"/>
-      <c r="N32" s="5" t="n"/>
-      <c r="O32" s="5" t="n"/>
-      <c r="P32" s="5" t="n"/>
-      <c r="Q32" s="5" t="n"/>
-      <c r="R32" s="5" t="n"/>
-      <c r="S32" s="5" t="n"/>
-      <c r="T32" s="5" t="n"/>
-      <c r="U32" s="5" t="n"/>
-      <c r="V32" s="13" t="n">
-        <v>30</v>
-      </c>
-      <c r="W32" s="5" t="n"/>
-      <c r="X32" s="5" t="n"/>
-    </row>
-    <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="11">
-        <f>IF(C33="","",COUNTA(C18:C33))</f>
-        <v/>
-      </c>
-      <c r="B33" s="5" t="n"/>
-      <c r="C33" s="12" t="inlineStr">
-        <is>
-          <t>중점 품질관리</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="n"/>
-      <c r="E33" s="5" t="n"/>
-      <c r="F33" s="5" t="n"/>
-      <c r="G33" s="5" t="n"/>
-      <c r="H33" s="5" t="n"/>
-      <c r="I33" s="5" t="n"/>
-      <c r="J33" s="5" t="n"/>
-      <c r="K33" s="5" t="n"/>
-      <c r="L33" s="5" t="n"/>
-      <c r="M33" s="5" t="n"/>
-      <c r="N33" s="5" t="n"/>
-      <c r="O33" s="5" t="n"/>
-      <c r="P33" s="5" t="n"/>
-      <c r="Q33" s="5" t="n"/>
-      <c r="R33" s="5" t="n"/>
-      <c r="S33" s="5" t="n"/>
-      <c r="T33" s="5" t="n"/>
-      <c r="U33" s="5" t="n"/>
-      <c r="V33" s="13" t="n">
-        <v>34</v>
-      </c>
-      <c r="W33" s="5" t="n"/>
-      <c r="X33" s="5" t="n"/>
-    </row>
-    <row r="34" ht="6" customHeight="1"/>
-    <row r="35" ht="10" customHeight="1"/>
-    <row r="36" ht="26" customHeight="1">
-      <c r="A36" s="14" t="n">
-        <v>46294</v>
-      </c>
-    </row>
-    <row r="37" ht="24" customHeight="1">
-      <c r="A37" s="15" t="inlineStr"/>
-      <c r="K37" s="16" t="inlineStr">
-        <is>
-          <t>품질관리자</t>
-        </is>
-      </c>
-      <c r="Q37" s="17" t="inlineStr">
-        <is>
-          <t>한품질</t>
-        </is>
-      </c>
-      <c r="U37" s="18" t="inlineStr">
-        <is>
-          <t>(서명 또는 인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="24" customHeight="1">
-      <c r="A38" s="15" t="inlineStr"/>
-      <c r="K38" s="16" t="inlineStr">
-        <is>
-          <t>현장대리인</t>
-        </is>
-      </c>
-      <c r="Q38" s="17" t="inlineStr">
-        <is>
-          <t>김철수</t>
-        </is>
-      </c>
-      <c r="U38" s="18" t="inlineStr">
-        <is>
-          <t>(서명 또는 인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="6" customHeight="1"/>
-    <row r="41" ht="19.5" customHeight="1">
-      <c r="A41" s="19" t="inlineStr">
-        <is>
-          <t>이 시트는 작성 예시입니다(가상의 현장 · 이름 · 금액). 실제로는 앞 시트에 적으세요.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="81">
-    <mergeCell ref="V24:X24"/>
-    <mergeCell ref="C23:U23"/>
-    <mergeCell ref="U38:X38"/>
-    <mergeCell ref="A3:X3"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="C18:U18"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="K38:P38"/>
-    <mergeCell ref="V22:X22"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="V21:X21"/>
-    <mergeCell ref="C20:U20"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="G12:X12"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="V23:X23"/>
-    <mergeCell ref="C22:U22"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="G7:X7"/>
-    <mergeCell ref="A38:J38"/>
-    <mergeCell ref="C32:U32"/>
-    <mergeCell ref="V27:X27"/>
-    <mergeCell ref="Q37:T37"/>
-    <mergeCell ref="V25:X25"/>
-    <mergeCell ref="C24:U24"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C33:U33"/>
-    <mergeCell ref="K37:P37"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="C26:U26"/>
-    <mergeCell ref="G9:X9"/>
-    <mergeCell ref="V17:X17"/>
-    <mergeCell ref="Q38:T38"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="C25:U25"/>
-    <mergeCell ref="G11:X11"/>
-    <mergeCell ref="A15:X15"/>
-    <mergeCell ref="V20:X20"/>
-    <mergeCell ref="V29:X29"/>
-    <mergeCell ref="V31:X31"/>
-    <mergeCell ref="A41:X41"/>
-    <mergeCell ref="G13:X13"/>
-    <mergeCell ref="V32:X32"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="V26:X26"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="V18:X18"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="V33:X33"/>
-    <mergeCell ref="U37:X37"/>
-    <mergeCell ref="V19:X19"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="V28:X28"/>
-    <mergeCell ref="C27:U27"/>
-    <mergeCell ref="C17:U17"/>
-    <mergeCell ref="G6:X6"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="V30:X30"/>
-    <mergeCell ref="C19:U19"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C28:U28"/>
-    <mergeCell ref="G5:X5"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C30:U30"/>
-    <mergeCell ref="C29:U29"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A37:J37"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C31:U31"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="M1:X1"/>
-    <mergeCell ref="C21:U21"/>
-    <mergeCell ref="A36:X36"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="G8:X8"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/web/public/forms/pumjil-gwanri-gyehoek.xlsx
+++ b/web/public/forms/pumjil-gwanri-gyehoek.xlsx
@@ -585,7 +585,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
